--- a/src/attributions/attributions_ig_traj_219.xlsx
+++ b/src/attributions/attributions_ig_traj_219.xlsx
@@ -1002,19 +1002,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2029285906775732</v>
+        <v>0.3057523227460114</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0489198425369044</v>
+        <v>0.06579167629790363</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2039069797821435</v>
+        <v>-0.2601915802061966</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -1023,55 +1023,55 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01382290575525684</v>
+        <v>0.02968277776807611</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002449478488282985</v>
+        <v>0.005423304434093882</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0442631625800613</v>
+        <v>0.04831272363754007</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>-0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01211027083294388</v>
+        <v>-0.1222037196172892</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.08874809981403427</v>
+        <v>-0.09282947229337751</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.03943152316872708</v>
+        <v>-0.1350358918814083</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
@@ -1080,22 +1080,22 @@
         <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.03112777673599575</v>
+        <v>0.119718367081547</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1204441421551671</v>
+        <v>0.05716150181979567</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.04790809052615605</v>
+        <v>0.1472858053044284</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -1104,40 +1104,40 @@
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.04818484970019409</v>
+        <v>0.120955653445357</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.04277794525325546</v>
+        <v>-0.05564058727457193</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.1195547718489098</v>
+        <v>-0.2355049025935752</v>
       </c>
       <c r="AQ2" t="n">
         <v>-0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.2433553909377797</v>
+        <v>0.6427071852819255</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1146,25 +1146,25 @@
         <v>-0</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.1476706980403516</v>
+        <v>-0.2523550040367366</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.3810584717826482</v>
+        <v>-0.4216575468079953</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.1207749947031511</v>
+        <v>0.1128562629496318</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,13 +1173,13 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.02615956116734798</v>
+        <v>0.06564242316416113</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.06621391016378995</v>
+        <v>-0.1645604742129381</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
         <v>-0</v>
@@ -1188,76 +1188,76 @@
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0001840758772916465</v>
+        <v>0.06596592720487399</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.02701159701704657</v>
+        <v>0.08780911047235011</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.01590446965451614</v>
+        <v>0.1642245428998055</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.06387948538210578</v>
+        <v>0.2162555667136201</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.1019661637218371</v>
+        <v>-0.102726014258895</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.1161547233751528</v>
+        <v>-0.2776585600512539</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
         <v>-0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.09999892273220937</v>
+        <v>-0.2562667729184678</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.02256445087727526</v>
+        <v>-0.06093926397851217</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.1114156746813355</v>
+        <v>0.1766194307047158</v>
       </c>
       <c r="CJ2" t="n">
         <v>0</v>
@@ -1266,58 +1266,58 @@
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.002618536853996481</v>
+        <v>-0.233475686560081</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
         <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.04480032653624928</v>
+        <v>0.05658685757637985</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.01230190190511231</v>
+        <v>0.143933765759135</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.08135667542982904</v>
+        <v>-0.2446523429804898</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01477688769894233</v>
+        <v>-0.05575568320706113</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.1251135891169797</v>
+        <v>0.1517969809323543</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
         <v>0</v>
@@ -1326,73 +1326,73 @@
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.04869346391191082</v>
+        <v>-0.1324954261874808</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.04670034693943906</v>
+        <v>-0.05048531141379477</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.004921230597223906</v>
+        <v>0.1371458580937623</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.0170690965166942</v>
+        <v>-0.08674429709316184</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.09762799927350577</v>
+        <v>0.007552348485462051</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.01651112157121482</v>
+        <v>0.07261903360331157</v>
       </c>
       <c r="DT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.04786376305129841</v>
+        <v>0.159260147069458</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ2" t="n">
         <v>0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.002466107036125797</v>
+        <v>-0.04484137452983293</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0.01062321062650451</v>
+        <v>0.1673148913369745</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1404,25 +1404,25 @@
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.1072336276855924</v>
+        <v>-0.1198412885971141</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.01160921830577171</v>
+        <v>-0.0864650391803147</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.1230465486167455</v>
+        <v>0.153367871689946</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>-0</v>
@@ -1431,10 +1431,10 @@
         <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.04786519836445473</v>
+        <v>-0.1693119702494127</v>
       </c>
       <c r="EQ2" t="n">
         <v>-0</v>
@@ -1443,37 +1443,37 @@
         <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.03713622642471926</v>
+        <v>-0.1895854796273398</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.06123291785697746</v>
+        <v>0.1621745883383629</v>
       </c>
       <c r="EU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.08002683643796135</v>
+        <v>-0.2347041410654898</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.02696689249196997</v>
+        <v>-0.1166271024937341</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.1144545931797553</v>
+        <v>0.1609001969343876</v>
       </c>
       <c r="FD2" t="n">
         <v>0</v>
@@ -1485,22 +1485,22 @@
         <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.07328578524471889</v>
+        <v>-0.1241926100016105</v>
       </c>
       <c r="FI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ2" t="n">
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.05502268613446842</v>
+        <v>-0.07009745179052719</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.128991699199469</v>
+        <v>0.2878688561545821</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
@@ -1512,58 +1512,58 @@
         <v>0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.1536573435632627</v>
+        <v>-0.008678678164605866</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.04836743607576374</v>
+        <v>0.06419936475337053</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.07015484150652893</v>
+        <v>0.05834805540727327</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.04359163589180996</v>
+        <v>-0.1165236057022418</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
         <v>0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0.02660780921729116</v>
+        <v>0.1928152609455519</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -2137,10 +2137,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06164528477532262</v>
+        <v>0.3723447833601671</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,25 +2149,25 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.00947181562570072</v>
+        <v>0.03270131570441095</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.02084134091931661</v>
+        <v>-0.1481132587545465</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008402246568090087</v>
+        <v>0.07806574086418649</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,43 +2176,43 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.001642007652415226</v>
+        <v>-0.0123789304044336</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.005576725341241475</v>
+        <v>-0.0474207524753178</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002505032973461024</v>
+        <v>0.1531175198803662</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.006786407708217594</v>
+        <v>-0.1393495340047074</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001086050619200524</v>
+        <v>-0.03251322459877232</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -2221,79 +2221,79 @@
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0118166067507868</v>
+        <v>0.02668232532783662</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02381388958612998</v>
+        <v>-0.2318199362577361</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.0008413102544217923</v>
+        <v>0.03641095460051185</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.003161421802135167</v>
+        <v>0.2001752736061113</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01248545679290628</v>
+        <v>0.1517265925466987</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.01638385987357694</v>
+        <v>-0.14776295440619</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.08167188550284556</v>
+        <v>0.7523265048028468</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.002983426838779252</v>
+        <v>-0.2236557542142625</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.005011874375008684</v>
+        <v>-0.1946416528082396</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.03076870170503649</v>
+        <v>-0.02013384261836163</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,25 +2311,25 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.02042812232900237</v>
+        <v>-0.07032665556398773</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.04950450233859762</v>
+        <v>-0.1123049925139021</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.03339932611301159</v>
+        <v>0.03469309981712113</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
@@ -2338,13 +2338,13 @@
         <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02317441788268359</v>
+        <v>0.1329383957358534</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.004460504489089329</v>
+        <v>0.157470095687143</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,7 +2356,7 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0286586207638927</v>
+        <v>0.3829288205992971</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,43 +2365,43 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.006181886832478472</v>
+        <v>-0.02554702847301625</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.003962433757637929</v>
+        <v>-0.2462874241705843</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.01835562934276924</v>
+        <v>-0.2470015968941225</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.001471314198837709</v>
+        <v>-0.03765293856164183</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.01874654599405379</v>
+        <v>0.1688854066205257</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
         <v>0</v>
@@ -2410,49 +2410,49 @@
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.008115025392112053</v>
+        <v>-0.1605812045751217</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
         <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.003892852275518035</v>
+        <v>0.0877320112976422</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0007763791134900563</v>
+        <v>-0.0004823473311048004</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT4" t="n">
         <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01397064473119442</v>
+        <v>-0.2229940873196077</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.003277750691518288</v>
+        <v>-0.0318494895672547</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.01864369185728248</v>
+        <v>0.1684761980209558</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
@@ -2464,52 +2464,52 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.004083767682804701</v>
+        <v>-0.0382963263445471</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
         <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.02423368004716522</v>
+        <v>-0.07715113876007045</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.003587403050199469</v>
+        <v>0.0391536105044364</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.003631185777059407</v>
+        <v>-0.1060452160158828</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>2.829028960275197e-05</v>
+        <v>-0.002280503920621933</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.005105422811569684</v>
+        <v>0.0101241945769894</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>-0</v>
@@ -2518,46 +2518,46 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.01291134167828595</v>
+        <v>0.09279946202944754</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.03098297264176144</v>
+        <v>-0.07920632051252594</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.000508662513114477</v>
+        <v>0.1261248261701846</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.01563837895745484</v>
+        <v>-0.05020222813408409</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.0004256991142169907</v>
+        <v>-0.1450857324674949</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01133111537309056</v>
+        <v>0.08032194995051321</v>
       </c>
       <c r="EL4" t="n">
         <v>-0</v>
@@ -2569,10 +2569,10 @@
         <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.01844991367882736</v>
+        <v>-0.1307088247943847</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
@@ -2581,37 +2581,37 @@
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.009148878918307549</v>
+        <v>-0.2127589826205118</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.005591449427534576</v>
+        <v>0.03934420998924418</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01719665210809002</v>
+        <v>-0.2461501097544718</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.004086736241996445</v>
+        <v>-0.07529357539274659</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.01990846078849886</v>
+        <v>0.1444772395630748</v>
       </c>
       <c r="FD4" t="n">
         <v>0</v>
@@ -2620,13 +2620,13 @@
         <v>-0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.001370416529415584</v>
+        <v>-0.2097378547464279</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,67 +2635,67 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.02718747500816612</v>
+        <v>0.07689302414421577</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.01927846596110732</v>
+        <v>0.2473284011354092</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.001412926287801983</v>
+        <v>-0.02881714120084175</v>
       </c>
       <c r="FR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0003343553842685277</v>
+        <v>-0.0008173531966460252</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.008361267083601616</v>
+        <v>0.1080102913238926</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02668185660748199</v>
+        <v>-0.09812784982167637</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.006945079661175605</v>
+        <v>0.1019689153658571</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1191637788464301</v>
+        <v>0.3778613044784142</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,13 +2718,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.000244472505624229</v>
+        <v>0.02849207907819654</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0775106720181679</v>
+        <v>-0.1836100948352341</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03302838053058574</v>
+        <v>0.1455419169676797</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,10 +2745,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0002387669203468907</v>
+        <v>-0.01419360066480611</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.03003977676142359</v>
+        <v>-0.07765334978164609</v>
       </c>
       <c r="P5" t="n">
         <v>-0</v>
@@ -2760,10 +2760,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.002284935655014759</v>
+        <v>0.1180120793323559</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2772,37 +2772,37 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.02285615139674775</v>
+        <v>-0.151815996269272</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.002035207997721834</v>
+        <v>-0.0286213852713408</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01466475381318209</v>
+        <v>0.05242708817068826</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02499733283907983</v>
+        <v>-0.2346623093466465</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.003625874880884475</v>
+        <v>-0.08678582768483063</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2817,22 +2817,22 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02024443533119928</v>
+        <v>0.1676093115223271</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.002488386176331627</v>
+        <v>0.1079944240206459</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.03683754671665188</v>
+        <v>-0.1103329200769282</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
@@ -2841,22 +2841,22 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1278014506336576</v>
+        <v>0.6652669174793525</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.01175623674190871</v>
+        <v>-0.1650130555279703</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.0900154314256542</v>
+        <v>-0.1918088033585739</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.05362211914798582</v>
+        <v>-0.005390590819121107</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,40 +2880,40 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.03211875218902337</v>
+        <v>-0.03662852657117052</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.06676288011334312</v>
+        <v>-0.1576517212884833</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.04458169923675846</v>
+        <v>0.04910847126916346</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02126862868062271</v>
+        <v>0.08784564411504185</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.007043322162713457</v>
+        <v>0.05081774320523187</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>0</v>
@@ -2922,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.04455691860171433</v>
+        <v>0.3173876833650052</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,13 +2934,13 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.003401293739031888</v>
+        <v>-0.0396185754647539</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.02467392885279949</v>
+        <v>-0.1429860922838909</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>-0</v>
@@ -2952,22 +2952,22 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.03511691291232748</v>
+        <v>-0.2230112104191768</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.004431916780775235</v>
+        <v>-0.03824753962087318</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.03606415395618955</v>
+        <v>0.1375414661742255</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
@@ -2979,73 +2979,73 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.004074752419878877</v>
+        <v>-0.133468630610159</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.009724712516633186</v>
+        <v>0.04810326481924673</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.003520570998939234</v>
+        <v>0.007859435166270499</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.03046445154678787</v>
+        <v>-0.2045450286298391</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0002365190742413883</v>
+        <v>-0.0352503407690993</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.03887609900341878</v>
+        <v>0.1461433650845621</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.01034247757987183</v>
+        <v>-0.05932880938322233</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.00813141640399475</v>
+        <v>-0.04206817422686795</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.005290865928317907</v>
+        <v>0.03767508732298684</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01676601883045015</v>
+        <v>-0.1202276270456558</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01100865933635951</v>
+        <v>-0.01570233707490479</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.008103463346265306</v>
+        <v>0.06758872960097351</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,19 +3087,19 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0129492763358943</v>
+        <v>0.02613499014974608</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02228210556374816</v>
+        <v>0.09186621841830427</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.001582632522033156</v>
+        <v>0.1407803128045796</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
@@ -3108,28 +3108,28 @@
         <v>-0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.0247554421519228</v>
+        <v>-0.04287318118774365</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.000471459209142786</v>
+        <v>-0.08342510944347767</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.02826041639991656</v>
+        <v>0.05427385247179062</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
@@ -3138,28 +3138,28 @@
         <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.02713202593662809</v>
+        <v>-0.1114991590851256</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.005385721609663822</v>
+        <v>-0.08860508754012039</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.03309245763536544</v>
+        <v>0.07296839794279883</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>0</v>
@@ -3168,34 +3168,34 @@
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.02705060628418314</v>
+        <v>-0.2268161139609564</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.002302468110360555</v>
+        <v>-0.05892538329875015</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.03650115454140639</v>
+        <v>0.1276088596143859</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.007137900638944977</v>
+        <v>-0.2431237035835043</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
@@ -3204,64 +3204,64 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.0255698564969661</v>
+        <v>0.07942028805398021</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01900989711617514</v>
+        <v>0.2388403238926852</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.005737293127769899</v>
+        <v>-0.0343818719065719</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.001099278822622304</v>
+        <v>-0.006156833086654549</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.02910416436813578</v>
+        <v>0.136569411252558</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02102059787942549</v>
+        <v>-0.04978062805638354</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.004307472663903668</v>
+        <v>0.02158113824724713</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3847,154 +3847,154 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2237328732943498</v>
+        <v>0.5915928228725817</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.06515417034618702</v>
+        <v>-0.02703904971993809</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04925240757766072</v>
+        <v>0.08599319928904407</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.08476463419001774</v>
+        <v>-0.237825335095307</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.113946609723205</v>
+        <v>0.4477958636757286</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04348223548823189</v>
+        <v>-0.115732078472011</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02053297659647814</v>
+        <v>-0.02416591850882351</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.03670406915433636</v>
+        <v>-0.09670599751248868</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04947635697741309</v>
+        <v>0.1672337308926944</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0155026513131434</v>
+        <v>-0.1730801486147821</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03229165502607485</v>
+        <v>-0.1562992695118425</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0278265653086327</v>
+        <v>0.006167786015266592</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01191232362629384</v>
+        <v>0.1326823582750994</v>
       </c>
       <c r="AD7" t="n">
         <v>-0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.04625124271083816</v>
+        <v>-0.3583078217787987</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.007114254808101944</v>
+        <v>-0.232765192223638</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0261174273394349</v>
+        <v>-0.1208615506671584</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.002666214520989679</v>
+        <v>0.2796811097213507</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.03086087095530536</v>
+        <v>-0.1420132545468101</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02184178988213995</v>
+        <v>0.1855140622374054</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.03432867370494121</v>
+        <v>-0.1993903488538412</v>
       </c>
       <c r="AQ7" t="n">
         <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.3227150389750425</v>
+        <v>0.864545694427319</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.007751379962732096</v>
+        <v>-0.009316265426709647</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0526009955330097</v>
+        <v>-0.1689379298351239</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.04119718507186194</v>
+        <v>-0.1561617112762206</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,58 +4003,58 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.03383296358613373</v>
+        <v>0.01679503937030948</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.04651532443530802</v>
+        <v>-0.1072122271818247</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.08118682525031878</v>
+        <v>-0.125129144069843</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.1414536344066122</v>
+        <v>-0.2593369916515429</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.07632378989844175</v>
+        <v>0.04420871583938941</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.04455902229673983</v>
+        <v>0.003950810730606918</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.07446637399510551</v>
+        <v>0.1409970762303681</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01559255748328089</v>
+        <v>0.01292197288663296</v>
       </c>
       <c r="BR7" t="n">
         <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
         <v>0</v>
@@ -4063,19 +4063,19 @@
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1145850201877866</v>
+        <v>0.401924531779132</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.02824704025963684</v>
+        <v>-0.09813528066541953</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.01016993953042968</v>
+        <v>0.003017374006007177</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.02534765932683216</v>
+        <v>-0.1821313840544908</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4084,28 +4084,28 @@
         <v>-0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.05771564292045581</v>
+        <v>-0.2894894678529111</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.004502205442877549</v>
+        <v>0.05270337809803905</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.002437689983302286</v>
+        <v>-0.07350026865210699</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.04911678631156369</v>
+        <v>0.129299637004917</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4114,109 +4114,109 @@
         <v>0</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02310077433991674</v>
+        <v>-0.2036905910701229</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.03296701065330334</v>
+        <v>0.1596578862146527</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.03164894325336205</v>
+        <v>0.0184589665216395</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.02088150581299981</v>
+        <v>0.0973130588115652</v>
       </c>
       <c r="CS7" t="n">
         <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.04980342204901105</v>
+        <v>-0.2651658720770109</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.02205934984653552</v>
+        <v>0.06204277344703473</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.002858505550361955</v>
+        <v>-0.08647788939643147</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0546092542740864</v>
+        <v>0.1277375875281912</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.01221774180187424</v>
+        <v>-0.04667460133478842</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.07270909583350729</v>
+        <v>-0.01751025877837298</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.01725989780393908</v>
+        <v>0.4670989354918933</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.005452412780540087</v>
+        <v>0.02414726860203964</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.02989548832981614</v>
+        <v>-0.1022234194423413</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.02975168509669514</v>
+        <v>0.05996840912381157</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.016942381946406</v>
+        <v>-0.1070851832848327</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.02395800829112853</v>
+        <v>0.1413922389906969</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>-0</v>
@@ -4225,190 +4225,190 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.01547217220507177</v>
+        <v>0.1552462539458248</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.0003033135218409532</v>
+        <v>0.07858529855686996</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.03729696935685564</v>
+        <v>-0.01287561130452411</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.004443582272796644</v>
+        <v>-0.01919168053910613</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.09215359024793898</v>
+        <v>-0.1240083848895802</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0357190691668179</v>
+        <v>0.08235209679429548</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.03803058930497912</v>
+        <v>-0.1113750297866926</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.01388623117169927</v>
+        <v>-0.03174695355072726</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.03423827687995525</v>
+        <v>-0.1218329449272588</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.005051869266449025</v>
+        <v>-0.06315923786977995</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.00201055681616478</v>
+        <v>-0.08506621150886014</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.07528214501248236</v>
+        <v>0.2533118520349926</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.04506702486800113</v>
+        <v>-0.3035134126702108</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.00546366305083414</v>
+        <v>0.06174690611041216</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01438115218192496</v>
+        <v>-0.1258363676875327</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.04543062448445263</v>
+        <v>0.1005455295567257</v>
       </c>
       <c r="FD7" t="n">
         <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.04039766155185378</v>
+        <v>-0.2252209711266066</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.02983183999575903</v>
+        <v>0.1450059309370776</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.0007851676876486605</v>
+        <v>-0.05643216118085478</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.01433026219893621</v>
+        <v>0.3725972217875037</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.008472526443757575</v>
+        <v>-0.1987113304785901</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.009498651053461057</v>
+        <v>0.2872777944503768</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.004007978858819655</v>
+        <v>0.001955805748718278</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0.0006667495878353233</v>
+        <v>0.09628168885746909</v>
       </c>
       <c r="FV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW7" t="n">
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03059570853169198</v>
+        <v>-0.1150369726107396</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.02431450821081933</v>
+        <v>-0.1620036778414712</v>
       </c>
       <c r="GC7" t="n">
         <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.00280911641239717</v>
+        <v>-0.07776944272891266</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4982,10 +4982,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.6366712051656227</v>
+        <v>-0.2221806683100062</v>
       </c>
       <c r="C9" t="n">
         <v>-0</v>
@@ -4994,13 +4994,13 @@
         <v>-0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08697509212496833</v>
+        <v>-0.00889114524676057</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9845505032661335</v>
+        <v>0.2071219026413123</v>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5009,10 +5009,10 @@
         <v>-0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2041022886760888</v>
+        <v>-0.08877588718342412</v>
       </c>
       <c r="L9" t="n">
         <v>-0</v>
@@ -5021,10 +5021,10 @@
         <v>-0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.07967963966601621</v>
+        <v>0.04478604186745562</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5597213971528552</v>
+        <v>0.1286645198798842</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
@@ -5039,22 +5039,22 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.08715578462065252</v>
+        <v>-0.08966617172079253</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
         <v>-0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1128410981611434</v>
+        <v>-0.008144594579350361</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02691143437295237</v>
+        <v>-0.03370216851146943</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -5066,19 +5066,19 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.2329839477389476</v>
+        <v>0.06395419421672134</v>
       </c>
       <c r="AD9" t="n">
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.01763307552341737</v>
+        <v>0.1431213228712825</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.1836191853288344</v>
+        <v>0.03843540805456153</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
@@ -5093,22 +5093,22 @@
         <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.07512987684999103</v>
+        <v>-0.1195672020171534</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.135831083578605</v>
+        <v>-0.08110743673424843</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.2797066560146976</v>
+        <v>0.1499306681790015</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.3741165585892315</v>
+        <v>-0.2996360635293902</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -5129,25 +5129,25 @@
         <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.356610395667373</v>
+        <v>0.06957098589022027</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.9361587589155737</v>
+        <v>0.1315384260110089</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.4424338738470506</v>
+        <v>0.1029697910086837</v>
       </c>
       <c r="BE9" t="n">
         <v>-0</v>
@@ -5156,25 +5156,25 @@
         <v>-0</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.1384431771571384</v>
+        <v>0.2152339857655745</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.1945064143017782</v>
+        <v>0.122901684707437</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0.1234283867715481</v>
+        <v>0.0289832139913838</v>
       </c>
       <c r="BN9" t="n">
         <v>0</v>
@@ -5183,10 +5183,10 @@
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.1181142808420209</v>
+        <v>-0.0555476991848121</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01576618077189797</v>
+        <v>-0.0558477689995262</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0.1934659202605951</v>
+        <v>-0.2176631160389566</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>-0</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.08962884748241209</v>
+        <v>-0.006294189550604892</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.3651984907511022</v>
+        <v>0.08621590065375564</v>
       </c>
       <c r="CA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.1955823356127975</v>
+        <v>0.1294020485609261</v>
       </c>
       <c r="CF9" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.00816970540163724</v>
+        <v>-0.01003754115683648</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0.1995026485597582</v>
+        <v>-0.08062827819193177</v>
       </c>
       <c r="CJ9" t="n">
         <v>0</v>
@@ -5249,25 +5249,25 @@
         <v>-0</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.01797619952919976</v>
+        <v>0.0754060753117639</v>
       </c>
       <c r="CO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP9" t="n">
         <v>0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.2259606775065933</v>
+        <v>-0.1454528902636138</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.1226291382239544</v>
+        <v>-0.03863716173996184</v>
       </c>
       <c r="CS9" t="n">
         <v>0</v>
@@ -5279,10 +5279,10 @@
         <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.1636802209639074</v>
+        <v>0.1215560049042346</v>
       </c>
       <c r="CX9" t="n">
         <v>-0</v>
@@ -5291,10 +5291,10 @@
         <v>-0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.05765584815094123</v>
+        <v>-0.005699454326810917</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0.234270734790426</v>
+        <v>-0.07379426942348548</v>
       </c>
       <c r="DB9" t="n">
         <v>-0</v>
@@ -5309,61 +5309,61 @@
         <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01350735563069386</v>
+        <v>-0.004458481497502783</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
         <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.2700888201685094</v>
+        <v>0.05275108982827627</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.03526955508469724</v>
+        <v>-0.007808168251972187</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.1382643363050792</v>
+        <v>0.01254057254252931</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.1018153573042857</v>
+        <v>0.01051363869718424</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.06027366733264448</v>
+        <v>-0.03530514319996934</v>
       </c>
       <c r="DT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.1310266696181392</v>
+        <v>-0.04886435877787023</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
@@ -5372,10 +5372,10 @@
         <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.3027254627391702</v>
+        <v>0.06151491881858998</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.1202720083068612</v>
+        <v>0.02188798943999884</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
@@ -5384,25 +5384,25 @@
         <v>-0</v>
       </c>
       <c r="EE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.08451005182699307</v>
+        <v>0.06679027795536686</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.1280852604447768</v>
+        <v>0.01562047184399274</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0.1644445508303873</v>
+        <v>-0.009264715892268242</v>
       </c>
       <c r="EL9" t="n">
         <v>0</v>
@@ -5411,40 +5411,40 @@
         <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.1665701240754379</v>
+        <v>0.1033089678227893</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.08792102926841404</v>
+        <v>0.07747313116232407</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.00308022753749505</v>
+        <v>0.0943310659010813</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.177007614638068</v>
+        <v>0.1354671311481852</v>
       </c>
       <c r="EZ9" t="n">
         <v>0</v>
@@ -5453,10 +5453,10 @@
         <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.05603850867091844</v>
+        <v>0.0002291822268167367</v>
       </c>
       <c r="FC9" t="n">
-        <v>-0.2370799297251215</v>
+        <v>-0.06437560627687069</v>
       </c>
       <c r="FD9" t="n">
         <v>0</v>
@@ -5468,10 +5468,10 @@
         <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0140750532655642</v>
+        <v>0.1204245175631809</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
@@ -5480,37 +5480,37 @@
         <v>0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.02253241486306879</v>
+        <v>-0.02566196495603158</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0.252454003355767</v>
+        <v>-0.1077820240306862</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0006296877171737042</v>
+        <v>0.1063617964989911</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
         <v>0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.1505408508105391</v>
+        <v>-0.008717879857046541</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0.3471022743025425</v>
+        <v>-0.06736844530401781</v>
       </c>
       <c r="FV9" t="n">
         <v>0</v>
@@ -5525,10 +5525,10 @@
         <v>-0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.1318251794098035</v>
+        <v>0.1135241997632618</v>
       </c>
       <c r="GA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB9" t="n">
         <v>0</v>
@@ -5537,7 +5537,7 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.07958104312441333</v>
+        <v>0.02004907915461063</v>
       </c>
       <c r="GE9" t="n">
         <v>0</v>
@@ -5551,22 +5551,22 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1318740611932359</v>
+        <v>0.5426926885220239</v>
       </c>
       <c r="C10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.005492943149031097</v>
+        <v>0.0216439644609442</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.09237698915256519</v>
+        <v>-0.2923418538645213</v>
       </c>
       <c r="G10" t="n">
         <v>-0</v>
@@ -5581,7 +5581,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.09435844624903741</v>
+        <v>0.5661190309108086</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,16 +5590,16 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.00387433263232507</v>
+        <v>-0.09563749562748579</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.05231596628413955</v>
+        <v>-0.1732764805130526</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
@@ -5608,7 +5608,7 @@
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.008302545337658861</v>
+        <v>0.1397605311519744</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,16 +5617,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01636179756816476</v>
+        <v>0.01367648753741331</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.01620105783673412</v>
+        <v>-0.1497068214381005</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -5635,19 +5635,19 @@
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.007877545156851748</v>
+        <v>-0.003526613107522172</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01256317973892767</v>
+        <v>-0.06849181379340162</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01658887695230819</v>
+        <v>0.09935494307920836</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -5662,22 +5662,22 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.005307641575658446</v>
+        <v>0.1727523325470297</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.01050052098194327</v>
+        <v>0.06534458083560532</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.04321017063011174</v>
+        <v>-0.09377243243483918</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,37 +5686,37 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1082364385961864</v>
+        <v>0.7312310865990951</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.008984154601010062</v>
+        <v>-0.2731384405480271</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.06027269610127131</v>
+        <v>-0.2909331629523529</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
         <v>-0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.05150394732376543</v>
+        <v>-0.1745625232477025</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,37 +5725,37 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.02408309547370742</v>
+        <v>0.005786022652157777</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.0588905221505984</v>
+        <v>-0.07462255900810361</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
         <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.04170675385584562</v>
+        <v>0.01556386561530482</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0149431797754241</v>
+        <v>0.07798829561103375</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01932360625396138</v>
+        <v>0.05339409097859832</v>
       </c>
       <c r="BR10" t="n">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.05519751872298534</v>
+        <v>0.4500287478261169</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -5779,10 +5779,10 @@
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.003424969247851455</v>
+        <v>-0.01561094248927397</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.02183011723430995</v>
+        <v>-0.1659425329872808</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5797,25 +5797,25 @@
         <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.02931573640885643</v>
+        <v>-0.2468026572995994</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.002823752722626449</v>
+        <v>0.01019721401887829</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02455424238017028</v>
+        <v>0.1116319612636757</v>
       </c>
       <c r="CJ10" t="n">
         <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL10" t="n">
         <v>0</v>
@@ -5824,61 +5824,61 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.00837748048736099</v>
+        <v>-0.08906866487965028</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.003916928761573623</v>
+        <v>0.08918441836054587</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.008731407320691024</v>
+        <v>0.03077762234635981</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.02153164021549675</v>
+        <v>-0.2337639456815072</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.002003978309657736</v>
+        <v>0.01062951206723477</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0303857761322393</v>
+        <v>0.1272685362638746</v>
       </c>
       <c r="DB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.004146839197418542</v>
+        <v>0.01319594562448032</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
@@ -5887,10 +5887,10 @@
         <v>-0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.007833888145544933</v>
+        <v>0.01862450382195774</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0131833482100878</v>
+        <v>0.1003835515782636</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
@@ -5902,28 +5902,28 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.01266161839795827</v>
+        <v>-0.07802572974572441</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.008747440187639103</v>
+        <v>-0.006917124975122394</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.004134410553009287</v>
+        <v>0.09378093681377034</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
@@ -5932,46 +5932,46 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.03638192622515123</v>
+        <v>-0.1401538117322314</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.00969916336586552</v>
+        <v>0.0645073818154584</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.01868138726598854</v>
+        <v>-0.1251596216932681</v>
       </c>
       <c r="EC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02008322058823762</v>
+        <v>-0.141545844024727</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.002968698146550201</v>
+        <v>-0.0573144815104106</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.01589273350073591</v>
+        <v>0.03738375968993004</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
@@ -5986,19 +5986,19 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.006071964025114669</v>
+        <v>0.1093431111161352</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.003405872680952868</v>
+        <v>0.01044666176605473</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.003510917546484083</v>
+        <v>-0.03806871826453082</v>
       </c>
       <c r="EU10" t="n">
         <v>0</v>
@@ -6007,58 +6007,58 @@
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
         <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.02109768676030957</v>
+        <v>-0.2680743063443463</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.001335814361383439</v>
+        <v>-0.01515814202184137</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.03096725298424894</v>
+        <v>0.1231524119663395</v>
       </c>
       <c r="FD10" t="n">
         <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.004398873560933414</v>
+        <v>-0.140885186080247</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.0162621825293441</v>
+        <v>-0.03966369495935109</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.02933338994252381</v>
+        <v>0.1121332542661675</v>
       </c>
       <c r="FM10" t="n">
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
         <v>0</v>
@@ -6067,7 +6067,7 @@
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.02071820846187045</v>
+        <v>-0.2392300522857213</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,37 +6076,37 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.02281204601385389</v>
+        <v>-0.07504610062722977</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.0008419326948454599</v>
+        <v>-0.006788029017868638</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.01337342822206208</v>
+        <v>-0.1129876723369952</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.02628249890962805</v>
+        <v>0.07090851134440188</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -6115,7 +6115,7 @@
         <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,16 +6123,16 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.4203970612742267</v>
+        <v>-0.3902375468267102</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2381725178332416</v>
+        <v>0.1878473641023177</v>
       </c>
       <c r="E11" t="n">
-        <v>0.273264130438886</v>
+        <v>0.08867952594288413</v>
       </c>
       <c r="F11" t="n">
         <v>-0</v>
@@ -6141,28 +6141,28 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3101477086637015</v>
+        <v>-0.4286505831184733</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2222121562054488</v>
+        <v>0.2669801854041424</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2696280773763496</v>
+        <v>0.1405202464332765</v>
       </c>
       <c r="O11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -6177,127 +6177,127 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1284318551118342</v>
+        <v>-0.04109162553456438</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01904545226727132</v>
+        <v>0.01533178623558822</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.07335317270094205</v>
+        <v>-0.0116301129691597</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>-0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.1704161127400031</v>
+        <v>-0.03030981253780318</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.05715818951733054</v>
+        <v>0.153763654368942</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.02356619343079017</v>
+        <v>-0.2217726761944828</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.04896102394264443</v>
+        <v>-0.1440833969953473</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.04477912547546925</v>
+        <v>0.04284552320016726</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.07869489294520983</v>
+        <v>-0.2331040469144822</v>
       </c>
       <c r="AP11" t="n">
         <v>-0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.3401131025108767</v>
+        <v>-0.2425030489364495</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.06970047537053838</v>
+        <v>0.181064099648297</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.008627081229880568</v>
+        <v>0.04343781030329023</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.008829065649101577</v>
+        <v>0.03074010019572927</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.2161857308369209</v>
+        <v>0.01945866673344017</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.3428484569850302</v>
+        <v>0.09399341976463066</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
@@ -6312,16 +6312,16 @@
         <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.09089568020081853</v>
+        <v>0.1097310862730086</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0.02630949504052616</v>
+        <v>0.07264371408636869</v>
       </c>
       <c r="BP11" t="n">
-        <v>-0.09840232868604756</v>
+        <v>-0.01118954949787514</v>
       </c>
       <c r="BQ11" t="n">
         <v>0</v>
@@ -6339,25 +6339,25 @@
         <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>-0.2637835255097385</v>
+        <v>-0.1862108689479959</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.005855053553077499</v>
+        <v>0.08266163169074263</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.04968715169096643</v>
+        <v>0.0009322462403479262</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC11" t="n">
         <v>-0</v>
@@ -6366,16 +6366,16 @@
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.0994917647820658</v>
+        <v>0.1947108411207845</v>
       </c>
       <c r="CF11" t="n">
         <v>0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0.05981657916910861</v>
+        <v>-0.06887845048790521</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.001654412517811515</v>
+        <v>-0.01049244579751373</v>
       </c>
       <c r="CI11" t="n">
         <v>0</v>
@@ -6393,19 +6393,19 @@
         <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.03904433531414777</v>
+        <v>0.09077372166627176</v>
       </c>
       <c r="CO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.08836504795522895</v>
+        <v>-0.08014811475072159</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.08395989053667714</v>
+        <v>-0.02544203126988138</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS11" t="n">
         <v>0</v>
@@ -6420,46 +6420,46 @@
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.09909492014780513</v>
+        <v>0.2097527983783143</v>
       </c>
       <c r="CX11" t="n">
         <v>-0</v>
       </c>
       <c r="CY11" t="n">
-        <v>-0.08172709137269067</v>
+        <v>-0.0736227543940539</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.01289019254973816</v>
+        <v>-0.0364095225089445</v>
       </c>
       <c r="DA11" t="n">
         <v>-0</v>
       </c>
       <c r="DB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
         <v>-0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.1913335792505671</v>
+        <v>0.1500866290529764</v>
       </c>
       <c r="DG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0.09039708995659418</v>
+        <v>-0.0391471973239022</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0.01612744328293991</v>
+        <v>0.0004639762198912587</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,25 +6468,25 @@
         <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.05315386549332303</v>
+        <v>0.09944575259077537</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.03945751839556569</v>
+        <v>-0.07080232137162867</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.07524115673016218</v>
+        <v>0.04003092691685088</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1090832463548563</v>
+        <v>0.04319991691164538</v>
       </c>
       <c r="DY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.1120631691043394</v>
+        <v>0.02552862267756187</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.04292370431063442</v>
+        <v>0.003611966123300141</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
         <v>-0</v>
@@ -6528,25 +6528,25 @@
         <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.06261320051121112</v>
+        <v>0.2200148816607372</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0.05128472242952131</v>
+        <v>-0.0515402049540205</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.1280042182459941</v>
+        <v>-0.04497360168235492</v>
       </c>
       <c r="EK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN11" t="n">
         <v>0</v>
@@ -6555,25 +6555,25 @@
         <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01090740335426707</v>
+        <v>-0.1175512243664153</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.03305469095304838</v>
+        <v>-0.01124282473495074</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.02963720384945741</v>
+        <v>0.01338937614481888</v>
       </c>
       <c r="ET11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
@@ -6582,16 +6582,16 @@
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.1021779611874328</v>
+        <v>0.2340009828994381</v>
       </c>
       <c r="EZ11" t="n">
         <v>0</v>
       </c>
       <c r="FA11" t="n">
-        <v>-0.07113789239965995</v>
+        <v>-0.0846230944567089</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.01393453093228759</v>
+        <v>-0.007484793920215041</v>
       </c>
       <c r="FC11" t="n">
         <v>0</v>
@@ -6600,52 +6600,52 @@
         <v>-0</v>
       </c>
       <c r="FE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.07244239177882095</v>
+        <v>0.08649804043931243</v>
       </c>
       <c r="FI11" t="n">
         <v>0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.1034012052979759</v>
+        <v>0.09156880849337438</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.05343306529002467</v>
+        <v>0.02003220934353154</v>
       </c>
       <c r="FL11" t="n">
         <v>0</v>
       </c>
       <c r="FM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.01786479763664515</v>
+        <v>0.1824214370626203</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.03866397923095361</v>
+        <v>0.01471591573657509</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.003043364984106816</v>
+        <v>-0.08443438783763341</v>
       </c>
       <c r="FU11" t="n">
         <v>0</v>
@@ -6654,37 +6654,37 @@
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
         <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.06642362777887707</v>
+        <v>0.1962122176105751</v>
       </c>
       <c r="GA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.06278896293088311</v>
+        <v>-0.005883491887675817</v>
       </c>
       <c r="GC11" t="n">
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE11" t="n">
         <v>0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4944175880602533</v>
+        <v>0.3673263660664046</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,16 +6701,16 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1198894349094563</v>
+        <v>-0.03132362115763966</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4544460008606231</v>
+        <v>-0.1574310961824845</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4274607518904434</v>
+        <v>0.4485034714310024</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,25 +6728,25 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.04888874850773579</v>
+        <v>-0.130178196493785</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4157528138401824</v>
+        <v>-0.1955038102499164</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04063933094066322</v>
+        <v>0.1181387580374067</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -6755,16 +6755,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.08967454752124288</v>
+        <v>-0.1505967697670783</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.01598316809495008</v>
+        <v>-0.008656607559602366</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,19 +6773,19 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.02252847513618931</v>
+        <v>-0.03162450802245122</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.008390708569729568</v>
+        <v>-0.2887825223557907</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.03544500394326719</v>
+        <v>0.003527479040623809</v>
       </c>
       <c r="AH12" t="n">
         <v>-0</v>
@@ -6800,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.08318877872611036</v>
+        <v>0.04767021123248868</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
@@ -6809,10 +6809,10 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.0007077278191615895</v>
+        <v>-0.05554508401760289</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.08540701532056351</v>
+        <v>0.01816034171727798</v>
       </c>
       <c r="AQ12" t="n">
         <v>-0</v>
@@ -6824,10 +6824,10 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4218259438604975</v>
+        <v>0.5191454181042116</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,16 +6836,16 @@
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.06897385573744649</v>
+        <v>-0.2773316772019603</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.2205919160920708</v>
+        <v>-0.1188790333326577</v>
       </c>
       <c r="AZ12" t="n">
         <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>0</v>
@@ -6854,7 +6854,7 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1099878069610339</v>
+        <v>-0.04339056641769333</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,52 +6863,52 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1555668212240102</v>
+        <v>-0.02496902837454742</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.2031233903851091</v>
+        <v>-0.08294885925804485</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1451342674025795</v>
+        <v>0.05824419041574769</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.002556688646453596</v>
+        <v>0.08937834520485273</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0211355153587851</v>
+        <v>-0.02766133106619291</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2207219932939731</v>
+        <v>0.280554085961145</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -6917,10 +6917,10 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.06717633274302381</v>
+        <v>-0.08484454530252006</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.129854641674758</v>
+        <v>-0.1133443628907627</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
@@ -6935,22 +6935,22 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.08697241061607046</v>
+        <v>-0.1241005857088528</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.005260933946613045</v>
+        <v>0.02982513345676222</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.1102993405917673</v>
+        <v>0.05788680263723674</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,49 +6962,49 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-4.43257607350541e-05</v>
+        <v>-0.1130418455220918</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.01466065102031537</v>
+        <v>0.1111120639927183</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.02412898156694127</v>
+        <v>0.09855759559282742</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.0687753690642883</v>
+        <v>-0.1207477986492186</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.001385798239291539</v>
+        <v>0.00912079538591205</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.1157981227674384</v>
+        <v>0.0813693175712514</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
@@ -7016,25 +7016,25 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.04431739291869521</v>
+        <v>-0.0540124289549061</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0469190519338525</v>
+        <v>-0.1975404969883628</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0004228659813447472</v>
+        <v>0.07982109192302066</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>0</v>
@@ -7043,19 +7043,19 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.006641109162840441</v>
+        <v>-0.02073396924641933</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.03409219115504388</v>
+        <v>-0.06329309576383095</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0.007839961212285225</v>
+        <v>0.08041025222081968</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7064,13 +7064,13 @@
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.05630551712360807</v>
+        <v>-0.0268568656386304</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
@@ -7079,25 +7079,25 @@
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01739268735557954</v>
+        <v>-0.0550253324327012</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.05349210144062201</v>
+        <v>0.04359670920676496</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.1002099334802206</v>
+        <v>-0.05013198736437276</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
@@ -7106,79 +7106,79 @@
         <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.02829821554655291</v>
+        <v>0.01336142295899115</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.1234794527568776</v>
+        <v>-0.006961048616991997</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.03354367535041377</v>
+        <v>-0.01249802592186753</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.01138240262551658</v>
+        <v>-0.005899383144940205</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.07389758701291133</v>
+        <v>0.1446168996258657</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.06650577815978947</v>
+        <v>-0.1419693449424611</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.00686835868898876</v>
+        <v>-0.0004515334052908549</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.1058259541203652</v>
+        <v>0.04850484575129888</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.005797606991718213</v>
+        <v>0.2021335913128045</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
@@ -7187,16 +7187,16 @@
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.008269053209006944</v>
+        <v>-0.07289011355661995</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.05044232467575337</v>
+        <v>0.1309518990581542</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
@@ -7205,46 +7205,46 @@
         <v>0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.005420703803291718</v>
+        <v>0.008538417899239708</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.008628367138022312</v>
+        <v>-0.02237659527608413</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.03001674149327355</v>
+        <v>-0.04848437542451323</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.04279250744070507</v>
+        <v>-0.03346134264582198</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.05313188342164341</v>
+        <v>0.08115448268945702</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1465852228526663</v>
+        <v>0.3969256418546411</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,25 +8408,25 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.07399542798630397</v>
+        <v>-0.01718061647502239</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0709790340585276</v>
+        <v>-0.1595186744597766</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1108856173884611</v>
+        <v>0.4372282952607412</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -8435,25 +8435,25 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.04595669083434802</v>
+        <v>-0.1139331941005722</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.06470193804116534</v>
+        <v>-0.1912269917031652</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01286623979709052</v>
+        <v>0.1044942959889899</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -8462,40 +8462,40 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.006100835549428585</v>
+        <v>-0.09466072415932646</v>
       </c>
       <c r="X15" t="n">
-        <v>0.009342836230473214</v>
+        <v>-0.02024099506776598</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.004928984544738137</v>
+        <v>-0.03685664010370459</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.01258156439247423</v>
+        <v>-0.2552359378293638</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01050107998378377</v>
+        <v>0.045977414084051</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
@@ -8507,22 +8507,22 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.009158633067053728</v>
+        <v>0.04261947115897059</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.009344143710511673</v>
+        <v>-0.03674726705645801</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.01452169277157193</v>
+        <v>0.004084694325702766</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8531,28 +8531,28 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1019198328055797</v>
+        <v>0.4298116403776999</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.02807047747016878</v>
+        <v>-0.266703631100383</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.02016552463268135</v>
+        <v>-0.1209157629426972</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>0</v>
@@ -8561,7 +8561,7 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.03040979956368515</v>
+        <v>-0.01793593956142691</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,52 +8570,52 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.05200338909831748</v>
+        <v>-0.006101564241852741</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.06011200255662029</v>
+        <v>-0.06069118740482153</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.03426528983123459</v>
+        <v>0.05052678002126591</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.01557273011220122</v>
+        <v>0.06157330246901688</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01534036555480199</v>
+        <v>-0.01112595399125816</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.047368182566852</v>
+        <v>0.2414822798158145</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
@@ -8624,10 +8624,10 @@
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.01165554142871243</v>
+        <v>-0.05985773466473071</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0.01167342535910132</v>
+        <v>-0.1240202384482711</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
@@ -8639,28 +8639,28 @@
         <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.02434920044063748</v>
+        <v>-0.1137540148714066</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.006277110844750866</v>
+        <v>0.02917904079566028</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.01747917093761229</v>
+        <v>0.05963678913299981</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
@@ -8669,7 +8669,7 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.0008711438210970087</v>
+        <v>-0.1147816444000389</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
@@ -8678,97 +8678,97 @@
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.004870258777359961</v>
+        <v>0.1496826747591614</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.01055356244104783</v>
+        <v>0.06868932225718427</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
         <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.01837875031968109</v>
+        <v>-0.1119537330061609</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.005788378002291633</v>
+        <v>0.01827083508161986</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.01825785415799794</v>
+        <v>0.08222235311554203</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.03055706956215015</v>
+        <v>-0.07805895886511502</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.04795676047248516</v>
+        <v>-0.2053762820890815</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.01313787130993649</v>
+        <v>0.06667956780340208</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.004916013979101529</v>
+        <v>-0.009997958543084565</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.01919661233951572</v>
+        <v>-0.06021135600141588</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0.007774198957988798</v>
+        <v>0.04169724196238191</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
@@ -8777,49 +8777,49 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.02846097191678534</v>
+        <v>-0.005631911990851824</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01360604075316584</v>
+        <v>-0.03638945139055259</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.01789462456361692</v>
+        <v>0.01366938329681499</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.02911864151567194</v>
+        <v>-0.05787979272810461</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.008480714679931127</v>
+        <v>0.01772311591468043</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.01387669463880132</v>
+        <v>0.002135051693077886</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
@@ -8828,22 +8828,22 @@
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.01260822431150292</v>
+        <v>-0.03440564933223574</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.003845554478425642</v>
+        <v>-0.01208967426754717</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.01036215508293767</v>
+        <v>0.1090035198219108</v>
       </c>
       <c r="EU15" t="n">
         <v>0</v>
@@ -8852,58 +8852,58 @@
         <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.01930000018848992</v>
+        <v>-0.1301528791426035</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.008683513147103507</v>
+        <v>0.002589470299987057</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.02122334911163535</v>
+        <v>0.04926107642619053</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.01604457638516874</v>
+        <v>0.1839387303034509</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.01197799151554985</v>
+        <v>-0.07780575109705781</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.01949669269291303</v>
+        <v>0.1383156177246908</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
@@ -8912,78 +8912,78 @@
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.0001186836000044023</v>
+        <v>0.002269034342212356</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.001333692896077636</v>
+        <v>-0.009107064464106952</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0182015524807463</v>
+        <v>-0.03162385840654541</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.0001952809621877177</v>
+        <v>-0.040712622699525</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
         <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.00411468136418883</v>
+        <v>0.0758062636767521</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
         <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.8502837428435279</v>
+        <v>-0.2632674171497739</v>
       </c>
       <c r="B16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05655871633976203</v>
+        <v>0.209488579268205</v>
       </c>
       <c r="F16" t="n">
-        <v>1.687231382981478</v>
+        <v>0.6283093612791977</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -8992,22 +8992,22 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4323332666266763</v>
+        <v>-0.16441393391849</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L16" t="n">
         <v>-0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1602354216972428</v>
+        <v>0.3905909750829961</v>
       </c>
       <c r="O16" t="n">
-        <v>1.278894506970289</v>
+        <v>1.067381410106608</v>
       </c>
       <c r="P16" t="n">
         <v>-0</v>
@@ -9019,52 +9019,52 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1922866802710226</v>
+        <v>0.08536340758348407</v>
       </c>
       <c r="T16" t="n">
         <v>-0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V16" t="n">
         <v>-0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5082619239813235</v>
+        <v>-0.02150163681497325</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1915377317545275</v>
+        <v>0.128464423379295</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.2231365369000803</v>
+        <v>-0.1540701535566233</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>-0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1062409241909324</v>
+        <v>0.02410445369008753</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.09126751785465746</v>
+        <v>-0.3189598640268801</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -9073,7 +9073,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.1899579490643113</v>
+        <v>-0.08704243343982818</v>
       </c>
       <c r="AL16" t="n">
         <v>-0</v>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01888882982903044</v>
+        <v>-0.3521654900326996</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.06123801101473281</v>
+        <v>-0.02474078680267843</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -9097,52 +9097,52 @@
         <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0.6097803001632807</v>
+        <v>-0.02157083022841234</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.6201411756746733</v>
+        <v>-0.2630871735945537</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.052831566551708</v>
+        <v>0.6539432702725795</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0.2060866365751479</v>
+        <v>-0.1945146997898888</v>
       </c>
       <c r="BD16" t="n">
         <v>-0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1354846950335468</v>
+        <v>0.5691703431710214</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.1952686044250534</v>
+        <v>-0.3498127435036994</v>
       </c>
       <c r="BI16" t="n">
         <v>-0</v>
@@ -9154,10 +9154,10 @@
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0.03870840396197738</v>
+        <v>0.1527822424762326</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
@@ -9166,40 +9166,40 @@
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.06466038365058653</v>
+        <v>0.03445941759659151</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.1143795097060027</v>
+        <v>0.02567225477356964</v>
       </c>
       <c r="BR16" t="n">
         <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT16" t="n">
         <v>-0</v>
       </c>
       <c r="BU16" t="n">
-        <v>-0.4089227988679115</v>
+        <v>-0.01203677852762843</v>
       </c>
       <c r="BV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.3257989605731144</v>
+        <v>-0.04024737753969684</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.6145798994091752</v>
+        <v>0.3525289303833425</v>
       </c>
       <c r="CA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="n">
         <v>-0</v>
@@ -9208,7 +9208,7 @@
         <v>-0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.2339331298305126</v>
+        <v>0.07345054580648686</v>
       </c>
       <c r="CE16" t="n">
         <v>-0</v>
@@ -9220,22 +9220,22 @@
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.03677137526617377</v>
+        <v>-0.04725116843565927</v>
       </c>
       <c r="CI16" t="n">
-        <v>-0.3353032623842591</v>
+        <v>-0.06039160539440133</v>
       </c>
       <c r="CJ16" t="n">
         <v>-0</v>
       </c>
       <c r="CK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
         <v>-0</v>
       </c>
       <c r="CM16" t="n">
-        <v>-0.01918928072767162</v>
+        <v>-0.0775998314595973</v>
       </c>
       <c r="CN16" t="n">
         <v>0</v>
@@ -9247,25 +9247,25 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.5706829987925043</v>
+        <v>-0.19300799013398</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.08236883473748149</v>
+        <v>0.270372402189268</v>
       </c>
       <c r="CS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.2203005068442297</v>
+        <v>0.08847749042046107</v>
       </c>
       <c r="CW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX16" t="n">
         <v>-0</v>
@@ -9274,10 +9274,10 @@
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.03393527105203356</v>
+        <v>-0.1431402407705024</v>
       </c>
       <c r="DA16" t="n">
-        <v>-0.3184503568692622</v>
+        <v>-0.1493073813460601</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
@@ -9286,64 +9286,64 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
-        <v>-0.001021463966942377</v>
+        <v>0.005702698874129549</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.4784050070619013</v>
+        <v>0.1655221300707579</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.04168057656363482</v>
+        <v>-0.1487924714087882</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
         <v>-0</v>
       </c>
       <c r="DM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.1183995626040507</v>
+        <v>0.02059958295346414</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP16" t="n">
         <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.1265712080371372</v>
+        <v>0.1345543001457302</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.09133203575488023</v>
+        <v>-0.1932710553984657</v>
       </c>
       <c r="DT16" t="n">
         <v>0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.05651170388601569</v>
+        <v>0.06870129930356661</v>
       </c>
       <c r="DX16" t="n">
         <v>-0</v>
@@ -9352,43 +9352,43 @@
         <v>0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.02092785148218939</v>
+        <v>-0.1085888242326713</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0.4458962471348428</v>
+        <v>-0.2807577804850698</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
         <v>-0</v>
       </c>
       <c r="EE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.150650987458159</v>
+        <v>-0.05828302996004474</v>
       </c>
       <c r="EG16" t="n">
         <v>-0</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI16" t="n">
         <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.1534375046047704</v>
+        <v>-0.1747669799486979</v>
       </c>
       <c r="EK16" t="n">
-        <v>-0.2033266677291174</v>
+        <v>-0.06677483701364652</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
@@ -9397,7 +9397,7 @@
         <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.08454460904624655</v>
+        <v>0.02145072903661248</v>
       </c>
       <c r="EP16" t="n">
         <v>-0</v>
@@ -9409,10 +9409,10 @@
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.3250134762032604</v>
+        <v>-0.09520561870017522</v>
       </c>
       <c r="ET16" t="n">
-        <v>-0.06627756881633352</v>
+        <v>-0.1823384893688573</v>
       </c>
       <c r="EU16" t="n">
         <v>-0</v>
@@ -9421,10 +9421,10 @@
         <v>-0</v>
       </c>
       <c r="EW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.187822665324337</v>
+        <v>0.04976585726261427</v>
       </c>
       <c r="EY16" t="n">
         <v>-0</v>
@@ -9436,94 +9436,94 @@
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.08804884683926674</v>
+        <v>-0.04071157965018422</v>
       </c>
       <c r="FC16" t="n">
-        <v>-0.2809320706643329</v>
+        <v>-0.1488192175556596</v>
       </c>
       <c r="FD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
-        <v>-0.09838211950112487</v>
+        <v>-0.1582405464879239</v>
       </c>
       <c r="FH16" t="n">
         <v>0</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.08654835641166246</v>
+        <v>-0.06669776593887092</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0.003487209481427227</v>
+        <v>-0.2664089717302998</v>
       </c>
       <c r="FM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.02852771258249955</v>
+        <v>0.02585028793104953</v>
       </c>
       <c r="FQ16" t="n">
         <v>0</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.004379587628498551</v>
+        <v>0.001954674052398164</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0.3123973185146371</v>
+        <v>-0.09633217170277589</v>
       </c>
       <c r="FV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX16" t="n">
         <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0.09610245220745987</v>
+        <v>-0.1617989115940726</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.05448303746657592</v>
+        <v>-0.09756517395285559</v>
       </c>
       <c r="GE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF16" t="n">
         <v>-0</v>
